--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rce5cb33336a649d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd56aef4ca2b4062"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ed9c311cf5147dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R703b056f24104a79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd56aef4ca2b4062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raf1ef7cdd4e34650"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R703b056f24104a79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40ea8f4b22654518"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raf1ef7cdd4e34650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7971bc82ee49419c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40ea8f4b22654518"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d0811049bac40fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7971bc82ee49419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1c66d211719b4566"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d0811049bac40fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc06e4fd3e5a4441"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1c66d211719b4566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R18095c1d14d44c85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc06e4fd3e5a4441"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7b4ac54ce0a4a76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R18095c1d14d44c85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raa3a1a2d53b240c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7b4ac54ce0a4a76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7858a0f812934b56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raa3a1a2d53b240c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8dbce73a40cc49f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7858a0f812934b56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R847a3180a5024524"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8dbce73a40cc49f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9e0e18a0059545ad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R847a3180a5024524"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f6cf212aaa54fb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9e0e18a0059545ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc5fe3dfdb10f42a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f6cf212aaa54fb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29ed9517ac684649"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc5fe3dfdb10f42a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6e5ca3cee6094a18"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29ed9517ac684649"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc6bcb012e294078"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6e5ca3cee6094a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R536b8735392c47c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc6bcb012e294078"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dcb913eda1d494e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R536b8735392c47c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R97b39eb0a5bd4ec3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dcb913eda1d494e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22238d52f48c4d84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R97b39eb0a5bd4ec3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf57fe60970db4552"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22238d52f48c4d84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09d6221b2bc84075"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf57fe60970db4552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rebfebbef1d764ff9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09d6221b2bc84075"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75e70817584c4e17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rebfebbef1d764ff9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re0af4a9260594dc8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75e70817584c4e17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3bdaf3dcb274111"/>
   </x:tableParts>
 </x:worksheet>
 </file>